--- a/03_Outputs/all/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/all/04_Cluster/Summary_Stats.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D2">
-        <v>-1.009293658750142E-17</v>
+        <v>3.573530360512223E-18</v>
       </c>
       <c r="E2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>-2.425997880485935</v>
+        <v>-8.736590198195003</v>
       </c>
       <c r="G2">
-        <v>1.192267133162733</v>
+        <v>0.570076350306586</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D3">
-        <v>-1.312081756375185E-16</v>
+        <v>2.925611142234885E-17</v>
       </c>
       <c r="E3">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F3">
-        <v>-1.464746934498695</v>
+        <v>-1.79314253114921</v>
       </c>
       <c r="G3">
-        <v>2.516330631057625</v>
+        <v>3.27492217455772</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D4">
-        <v>1.816728585750256E-16</v>
+        <v>1.843642426224701E-17</v>
       </c>
       <c r="E4">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>-1.885484094023963</v>
+        <v>-2.568004782381657</v>
       </c>
       <c r="G4">
-        <v>1.671610470368253</v>
+        <v>2.338950246282719</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D5">
-        <v>-2.119516683375299E-16</v>
+        <v>2.270156718858773E-17</v>
       </c>
       <c r="E5">
         <v>0.9999999999999999</v>
       </c>
       <c r="F5">
-        <v>-2.245325559812697</v>
+        <v>-2.676226615379074</v>
       </c>
       <c r="G5">
-        <v>2.088354401300649</v>
+        <v>2.989090349946454</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D6">
-        <v>7.569702440626068E-17</v>
+        <v>-8.432490816723259E-18</v>
       </c>
       <c r="E6">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>-1.429764574405501</v>
+        <v>-3.377657438923357</v>
       </c>
       <c r="G6">
-        <v>2.375705545758349</v>
+        <v>2.718449139215524</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D7">
-        <v>6.055761952500853E-17</v>
+        <v>2.202578397447752E-17</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>-1.901699202863841</v>
+        <v>-3.249702474870532</v>
       </c>
       <c r="G7">
-        <v>2.171385795354605</v>
+        <v>2.80318936990205</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D8">
-        <v>3.532527805625498E-17</v>
+        <v>-2.145012683099634E-18</v>
       </c>
       <c r="E8">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>-1.614588356844653</v>
+        <v>-3.47062216708017</v>
       </c>
       <c r="G8">
-        <v>2.931052031813679</v>
+        <v>4.171809563477858</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D9">
-        <v>1.025063872168113E-17</v>
+        <v>-5.457223214988538E-18</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F9">
-        <v>-0.5109403817858122</v>
+        <v>-1.335422301040694</v>
       </c>
       <c r="G9">
-        <v>4.415060871745471</v>
+        <v>10.15602168524787</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D10">
-        <v>5.096932976688219E-16</v>
+        <v>1.131039706336878E-18</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F10">
-        <v>-2.299034376137603</v>
+        <v>-4.216579492924282</v>
       </c>
       <c r="G10">
-        <v>1.954527599536878</v>
+        <v>1.415016166418096</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D11">
-        <v>-1.91765795162527E-16</v>
+        <v>-1.328798182598234E-18</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F11">
-        <v>-1.656799540306184</v>
+        <v>-2.687799830217598</v>
       </c>
       <c r="G11">
-        <v>1.532466053843609</v>
+        <v>3.149438304257335</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D12">
-        <v>2.018587317500285E-16</v>
+        <v>-1.773928226533883E-17</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>-1.248259406014539</v>
+        <v>-1.956045892917402</v>
       </c>
       <c r="G12">
-        <v>2.329263374587369</v>
+        <v>3.96815963947509</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D13">
-        <v>1.009293658750142E-16</v>
+        <v>-8.646078644702903E-18</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>-1.619918890964007</v>
+        <v>-2.529225657869897</v>
       </c>
       <c r="G13">
-        <v>1.852831475537608</v>
+        <v>3.361539269928816</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D14">
-        <v>2.119516683375299E-16</v>
+        <v>-1.32932402065189E-17</v>
       </c>
       <c r="E14">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>-2.2190116646</v>
+        <v>-1.852270485811725</v>
       </c>
       <c r="G14">
-        <v>1.322996042481685</v>
+        <v>5.872051834822624</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D15">
-        <v>-4.415659757031872E-17</v>
+        <v>1.760766012159909E-17</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F15">
-        <v>-1.570485058396011</v>
+        <v>-1.766259700036685</v>
       </c>
       <c r="G15">
-        <v>1.529252408826315</v>
+        <v>3.080547887796542</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D16">
-        <v>1.614869854000228E-16</v>
+        <v>-1.282220857268257E-17</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F16">
-        <v>-2.569433624248875</v>
+        <v>-3.483999295952195</v>
       </c>
       <c r="G16">
-        <v>1.63495048407373</v>
+        <v>2.346393885941261</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D17">
-        <v>-2.018587317500285E-17</v>
+        <v>-1.265133831029885E-17</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F17">
-        <v>-1.546502805907696</v>
+        <v>-2.456126084318659</v>
       </c>
       <c r="G17">
-        <v>2.319453847263542</v>
+        <v>4.665311989065715</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D18">
-        <v>-2.018587317500284E-16</v>
+        <v>2.252364961208286E-17</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F18">
-        <v>-2.538484034943318</v>
+        <v>-2.79908406316295</v>
       </c>
       <c r="G18">
-        <v>1.310343375486137</v>
+        <v>2.91251939631592</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D19">
-        <v>-5.046468293750711E-17</v>
+        <v>2.35527743142061E-17</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>-2.427059471236581</v>
+        <v>-5.091141056562349</v>
       </c>
       <c r="G19">
-        <v>1.568984861916797</v>
+        <v>2.506776490831638</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D20">
-        <v>2.523234146875356E-17</v>
+        <v>-3.106672905039964E-18</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>-2.269908414444483</v>
+        <v>-3.53749257433838</v>
       </c>
       <c r="G20">
-        <v>1.515216881226998</v>
+        <v>2.78196434428297</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D21">
-        <v>3.633457171500513E-16</v>
+        <v>-2.271967336486824E-17</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>-1.738285918071531</v>
+        <v>-3.812198855986544</v>
       </c>
       <c r="G21">
-        <v>2.07396025737248</v>
+        <v>2.827916595898227</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D22">
-        <v>-9.08364292875128E-17</v>
+        <v>-8.222589276130066E-18</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>-1.923543425410126</v>
+        <v>-4.054776522940765</v>
       </c>
       <c r="G22">
-        <v>2.039363534721254</v>
+        <v>2.176683680679193</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D23">
-        <v>7.569702440626067E-17</v>
+        <v>1.408248517797972E-17</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>-1.869447815147661</v>
+        <v>-2.358897378628837</v>
       </c>
       <c r="G23">
-        <v>1.856349357734679</v>
+        <v>2.861245578118104</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D24">
-        <v>7.065055611250996E-17</v>
+        <v>1.674593623490761E-17</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>-3.053747979702225</v>
+        <v>-3.378910429378913</v>
       </c>
       <c r="G24">
-        <v>1.743187725338075</v>
+        <v>2.810856373638918</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D25">
-        <v>-4.440892098500626E-16</v>
+        <v>8.049116928532385E-19</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>-1.363683774832632</v>
+        <v>-2.961308580693609</v>
       </c>
       <c r="G25">
-        <v>1.918854911631257</v>
+        <v>1.856993223569488</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D26">
-        <v>3.027880976250427E-17</v>
+        <v>1.847046821046306E-18</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F26">
-        <v>-2.064829789047005</v>
+        <v>-2.054611080772094</v>
       </c>
       <c r="G26">
-        <v>1.624233134082798</v>
+        <v>2.460948688602503</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D27">
-        <v>-7.998652245594878E-16</v>
+        <v>-1.88408316725841E-17</v>
       </c>
       <c r="E27">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>-1.437006464188384</v>
+        <v>-5.536870042191997</v>
       </c>
       <c r="G27">
-        <v>2.361291707510999</v>
+        <v>0.6742770223226823</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D28">
-        <v>-2.018587317500285E-17</v>
+        <v>4.439807896328141E-18</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>-1.013447046560743</v>
+        <v>-3.895667876609284</v>
       </c>
       <c r="G28">
-        <v>2.267492478119101</v>
+        <v>3.473744060831262</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D29">
-        <v>1.211152390500171E-16</v>
+        <v>-2.270926502401238E-17</v>
       </c>
       <c r="E29">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>-1.448603358368944</v>
+        <v>-1.898345467200467</v>
       </c>
       <c r="G29">
-        <v>2.174284104802546</v>
+        <v>3.402298193851278</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D30">
-        <v>6.055761952500853E-17</v>
+        <v>7.909254848281755E-19</v>
       </c>
       <c r="E30">
         <v>0.9999999999999999</v>
       </c>
       <c r="F30">
-        <v>-1.813834765996074</v>
+        <v>-3.607037124529915</v>
       </c>
       <c r="G30">
-        <v>3.200105174907554</v>
+        <v>2.347056830336199</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D31">
-        <v>-3.027880976250427E-16</v>
+        <v>-7.17655102011605E-18</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>-1.653423711067368</v>
+        <v>-3.955385643442785</v>
       </c>
       <c r="G31">
-        <v>1.745058586135704</v>
+        <v>1.525145077839005</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D32">
-        <v>8.578996099376209E-17</v>
+        <v>-5.46828207714789E-18</v>
       </c>
       <c r="E32">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>-1.450547055695796</v>
+        <v>-1.590213221935761</v>
       </c>
       <c r="G32">
-        <v>2.066485962284576</v>
+        <v>3.056942539512557</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D33">
-        <v>8.074349270001139E-17</v>
+        <v>1.380145997487148E-17</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F33">
-        <v>-1.834671361908434</v>
+        <v>-2.522157065559847</v>
       </c>
       <c r="G33">
-        <v>1.96036784281024</v>
+        <v>1.770429977299429</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/all/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/all/04_Cluster/Summary_Stats.xlsx
@@ -406,16 +406,16 @@
         <v>125</v>
       </c>
       <c r="D2">
-        <v>3.573530360512223E-18</v>
+        <v>5.287437154777308E-18</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F2">
-        <v>-8.736590198195003</v>
+        <v>-8.736590198195001</v>
       </c>
       <c r="G2">
-        <v>0.570076350306586</v>
+        <v>0.5700763503065861</v>
       </c>
     </row>
     <row r="3">
@@ -433,10 +433,10 @@
         <v>125</v>
       </c>
       <c r="D3">
-        <v>2.925611142234885E-17</v>
+        <v>1.848651440261584E-17</v>
       </c>
       <c r="E3">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>-1.79314253114921</v>
@@ -460,16 +460,16 @@
         <v>125</v>
       </c>
       <c r="D4">
-        <v>1.843642426224701E-17</v>
+        <v>-3.866481787517806E-18</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F4">
         <v>-2.568004782381657</v>
       </c>
       <c r="G4">
-        <v>2.338950246282719</v>
+        <v>2.338950246282721</v>
       </c>
     </row>
     <row r="5">
@@ -487,16 +487,16 @@
         <v>125</v>
       </c>
       <c r="D5">
-        <v>2.270156718858773E-17</v>
+        <v>-2.337084518966304E-17</v>
       </c>
       <c r="E5">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>-2.676226615379074</v>
+        <v>-2.676226615379075</v>
       </c>
       <c r="G5">
-        <v>2.989090349946454</v>
+        <v>2.989090349946458</v>
       </c>
     </row>
     <row r="6">
@@ -514,16 +514,16 @@
         <v>125</v>
       </c>
       <c r="D6">
-        <v>-8.432490816723259E-18</v>
+        <v>3.17280923756158E-17</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>-3.377657438923357</v>
+        <v>-3.377657438923359</v>
       </c>
       <c r="G6">
-        <v>2.718449139215524</v>
+        <v>2.718449139215523</v>
       </c>
     </row>
     <row r="7">
@@ -541,16 +541,16 @@
         <v>125</v>
       </c>
       <c r="D7">
-        <v>2.202578397447752E-17</v>
+        <v>5.767955557622884E-18</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>-3.249702474870532</v>
+        <v>-3.249702474870527</v>
       </c>
       <c r="G7">
-        <v>2.80318936990205</v>
+        <v>2.803189369902059</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>125</v>
       </c>
       <c r="D8">
-        <v>-2.145012683099634E-18</v>
+        <v>-2.929896451321634E-17</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F8">
-        <v>-3.47062216708017</v>
+        <v>-3.470622167080167</v>
       </c>
       <c r="G8">
-        <v>4.171809563477858</v>
+        <v>4.171809563477854</v>
       </c>
     </row>
     <row r="9">
@@ -595,10 +595,10 @@
         <v>125</v>
       </c>
       <c r="D9">
-        <v>-5.457223214988538E-18</v>
+        <v>4.3829957024899E-18</v>
       </c>
       <c r="E9">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>-1.335422301040694</v>
@@ -622,16 +622,16 @@
         <v>125</v>
       </c>
       <c r="D10">
-        <v>1.131039706336878E-18</v>
+        <v>-2.194772141805856E-17</v>
       </c>
       <c r="E10">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>-4.216579492924282</v>
+        <v>-4.216579492924284</v>
       </c>
       <c r="G10">
-        <v>1.415016166418096</v>
+        <v>1.415016166418095</v>
       </c>
     </row>
     <row r="11">
@@ -649,16 +649,16 @@
         <v>125</v>
       </c>
       <c r="D11">
-        <v>-1.328798182598234E-18</v>
+        <v>1.665334536937735E-18</v>
       </c>
       <c r="E11">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>-2.687799830217598</v>
+        <v>-2.687799830217599</v>
       </c>
       <c r="G11">
-        <v>3.149438304257335</v>
+        <v>3.149438304257332</v>
       </c>
     </row>
     <row r="12">
@@ -676,13 +676,13 @@
         <v>125</v>
       </c>
       <c r="D12">
-        <v>-1.773928226533883E-17</v>
+        <v>1.799688870152138E-17</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>-1.956045892917402</v>
+        <v>-1.956045892917401</v>
       </c>
       <c r="G12">
         <v>3.96815963947509</v>
@@ -703,16 +703,16 @@
         <v>125</v>
       </c>
       <c r="D13">
-        <v>-8.646078644702903E-18</v>
+        <v>2.929514270055833E-18</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>-2.529225657869897</v>
+        <v>-2.529225657869898</v>
       </c>
       <c r="G13">
-        <v>3.361539269928816</v>
+        <v>3.361539269928818</v>
       </c>
     </row>
     <row r="14">
@@ -730,16 +730,16 @@
         <v>125</v>
       </c>
       <c r="D14">
-        <v>-1.32932402065189E-17</v>
+        <v>1.818781670409608E-17</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>-1.852270485811725</v>
+        <v>-1.852270485811728</v>
       </c>
       <c r="G14">
-        <v>5.872051834822624</v>
+        <v>5.87205183482262</v>
       </c>
     </row>
     <row r="15">
@@ -757,13 +757,13 @@
         <v>125</v>
       </c>
       <c r="D15">
-        <v>1.760766012159909E-17</v>
+        <v>-8.218686148309118E-18</v>
       </c>
       <c r="E15">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>-1.766259700036685</v>
+        <v>-1.766259700036686</v>
       </c>
       <c r="G15">
         <v>3.080547887796542</v>
@@ -784,7 +784,7 @@
         <v>125</v>
       </c>
       <c r="D16">
-        <v>-1.282220857268257E-17</v>
+        <v>-1.558475570817563E-17</v>
       </c>
       <c r="E16">
         <v>0.9999999999999999</v>
@@ -811,16 +811,16 @@
         <v>125</v>
       </c>
       <c r="D17">
-        <v>-1.265133831029885E-17</v>
+        <v>5.695964533369846E-18</v>
       </c>
       <c r="E17">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>-2.456126084318659</v>
+        <v>-2.456126084318663</v>
       </c>
       <c r="G17">
-        <v>4.665311989065715</v>
+        <v>4.665311989065708</v>
       </c>
     </row>
     <row r="18">
@@ -838,16 +838,16 @@
         <v>125</v>
       </c>
       <c r="D18">
-        <v>2.252364961208286E-17</v>
+        <v>1.067505459029228E-17</v>
       </c>
       <c r="E18">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>-2.79908406316295</v>
+        <v>-2.799084063162949</v>
       </c>
       <c r="G18">
-        <v>2.91251939631592</v>
+        <v>2.912519396315923</v>
       </c>
     </row>
     <row r="19">
@@ -865,16 +865,16 @@
         <v>125</v>
       </c>
       <c r="D19">
-        <v>2.35527743142061E-17</v>
+        <v>1.632548263241773E-17</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F19">
-        <v>-5.091141056562349</v>
+        <v>-5.09114105656235</v>
       </c>
       <c r="G19">
-        <v>2.506776490831638</v>
+        <v>2.506776490831642</v>
       </c>
     </row>
     <row r="20">
@@ -892,16 +892,16 @@
         <v>125</v>
       </c>
       <c r="D20">
-        <v>-3.106672905039964E-18</v>
+        <v>-3.707320908596934E-18</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F20">
-        <v>-3.53749257433838</v>
+        <v>-3.537492574338383</v>
       </c>
       <c r="G20">
-        <v>2.78196434428297</v>
+        <v>2.781964344282971</v>
       </c>
     </row>
     <row r="21">
@@ -919,16 +919,16 @@
         <v>125</v>
       </c>
       <c r="D21">
-        <v>-2.271967336486824E-17</v>
+        <v>3.739196452468008E-18</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>-3.812198855986544</v>
+        <v>-3.812198855986547</v>
       </c>
       <c r="G21">
-        <v>2.827916595898227</v>
+        <v>2.827916595898226</v>
       </c>
     </row>
     <row r="22">
@@ -946,13 +946,13 @@
         <v>125</v>
       </c>
       <c r="D22">
-        <v>-8.222589276130066E-18</v>
+        <v>-3.092144595928659E-18</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F22">
-        <v>-4.054776522940765</v>
+        <v>-4.054776522940761</v>
       </c>
       <c r="G22">
         <v>2.176683680679193</v>
@@ -973,7 +973,7 @@
         <v>125</v>
       </c>
       <c r="D23">
-        <v>1.408248517797972E-17</v>
+        <v>1.619798045693344E-17</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -982,7 +982,7 @@
         <v>-2.358897378628837</v>
       </c>
       <c r="G23">
-        <v>2.861245578118104</v>
+        <v>2.861245578118102</v>
       </c>
     </row>
     <row r="24">
@@ -1000,16 +1000,16 @@
         <v>125</v>
       </c>
       <c r="D24">
-        <v>1.674593623490761E-17</v>
+        <v>-1.375657400493058E-17</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F24">
-        <v>-3.378910429378913</v>
+        <v>-3.378910429378874</v>
       </c>
       <c r="G24">
-        <v>2.810856373638918</v>
+        <v>2.810856373638819</v>
       </c>
     </row>
     <row r="25">
@@ -1027,13 +1027,13 @@
         <v>125</v>
       </c>
       <c r="D25">
-        <v>8.049116928532385E-19</v>
+        <v>2.081668171172169E-17</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>-2.961308580693609</v>
+        <v>-2.961308580693608</v>
       </c>
       <c r="G25">
         <v>1.856993223569488</v>
@@ -1054,16 +1054,16 @@
         <v>125</v>
       </c>
       <c r="D26">
-        <v>1.847046821046306E-18</v>
+        <v>2.791907330323973E-17</v>
       </c>
       <c r="E26">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>-2.054611080772094</v>
+        <v>-2.054611080772093</v>
       </c>
       <c r="G26">
-        <v>2.460948688602503</v>
+        <v>2.460948688602504</v>
       </c>
     </row>
     <row r="27">
@@ -1081,16 +1081,16 @@
         <v>125</v>
       </c>
       <c r="D27">
-        <v>-1.88408316725841E-17</v>
+        <v>-9.001480116843652E-18</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>-5.536870042191997</v>
+        <v>-5.536870042191994</v>
       </c>
       <c r="G27">
-        <v>0.6742770223226823</v>
+        <v>0.674277022322684</v>
       </c>
     </row>
     <row r="28">
@@ -1108,13 +1108,13 @@
         <v>125</v>
       </c>
       <c r="D28">
-        <v>4.439807896328141E-18</v>
+        <v>-2.984591740418096E-18</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F28">
-        <v>-3.895667876609284</v>
+        <v>-3.895667876609283</v>
       </c>
       <c r="G28">
         <v>3.473744060831262</v>
@@ -1135,10 +1135,10 @@
         <v>125</v>
       </c>
       <c r="D29">
-        <v>-2.270926502401238E-17</v>
+        <v>1.729931302374421E-17</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F29">
         <v>-1.898345467200467</v>
@@ -1162,10 +1162,10 @@
         <v>125</v>
       </c>
       <c r="D30">
-        <v>7.909254848281755E-19</v>
+        <v>-1.630997854135119E-17</v>
       </c>
       <c r="E30">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F30">
         <v>-3.607037124529915</v>
@@ -1189,16 +1189,16 @@
         <v>125</v>
       </c>
       <c r="D31">
-        <v>-7.17655102011605E-18</v>
+        <v>3.117645031025518E-17</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>-3.955385643442785</v>
+        <v>-3.955385643442784</v>
       </c>
       <c r="G31">
-        <v>1.525145077839005</v>
+        <v>1.525145077839008</v>
       </c>
     </row>
     <row r="32">
@@ -1216,7 +1216,7 @@
         <v>125</v>
       </c>
       <c r="D32">
-        <v>-5.46828207714789E-18</v>
+        <v>-8.411674135011538E-18</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -1225,7 +1225,7 @@
         <v>-1.590213221935761</v>
       </c>
       <c r="G32">
-        <v>3.056942539512557</v>
+        <v>3.056942539512555</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1243,16 @@
         <v>125</v>
       </c>
       <c r="D33">
-        <v>1.380145997487148E-17</v>
+        <v>1.931441118152577E-17</v>
       </c>
       <c r="E33">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>-2.522157065559847</v>
+        <v>-2.716952867028563</v>
       </c>
       <c r="G33">
-        <v>1.770429977299429</v>
+        <v>1.771439386181391</v>
       </c>
     </row>
   </sheetData>
